--- a/10. Sistemas de gestion empresarial/ConteoDeImpuntualidad.xlsx
+++ b/10. Sistemas de gestion empresarial/ConteoDeImpuntualidad.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cheng\Desktop\2DAM\10. Sistemas de gestion empresarial\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6A43F83-8EB9-474C-B805-9F2F21697728}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66B9BA23-3668-412D-9322-5D75E092CAA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4275" yWindow="5535" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Horas trabajadas" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="13">
   <si>
     <t>Total</t>
   </si>
@@ -64,9 +64,6 @@
   </si>
   <si>
     <t xml:space="preserve">     Mitchell Admin</t>
-  </si>
-  <si>
-    <t>Gráfico que muestra el conteo de veces que cada empleado ha fichado después de la hora de entrada esperada.</t>
   </si>
 </sst>
 </file>
@@ -138,50 +135,1152 @@
 </styleSheet>
 </file>
 
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Impuntualidad 2025</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Horas trabajadas'!$B$1:$B$3</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>noviembre 2025</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Número</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'Horas trabajadas'!$A$4:$A$16</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>('Horas trabajadas'!$A$4:$A$5,'Horas trabajadas'!$A$7,'Horas trabajadas'!$A$9,'Horas trabajadas'!$A$11,'Horas trabajadas'!$A$15)</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>     Abigail Peterson</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>     Anita Oliver</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>     Jennie Fletcher</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>     Marc Demo</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>     Mitchell Admin</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'Horas trabajadas'!$B$4:$B$16</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>('Horas trabajadas'!$B$4:$B$5,'Horas trabajadas'!$B$7,'Horas trabajadas'!$B$9,'Horas trabajadas'!$B$11,'Horas trabajadas'!$B$15)</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-E08F-41B4-9714-B12A15B28021}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Horas trabajadas'!$C$1:$C$3</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>diciembre 2025</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Número</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'Horas trabajadas'!$A$4:$A$16</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>('Horas trabajadas'!$A$4:$A$5,'Horas trabajadas'!$A$7,'Horas trabajadas'!$A$9,'Horas trabajadas'!$A$11,'Horas trabajadas'!$A$15)</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>     Abigail Peterson</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>     Anita Oliver</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>     Jennie Fletcher</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>     Marc Demo</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>     Mitchell Admin</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'Horas trabajadas'!$C$4:$C$16</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>('Horas trabajadas'!$C$4:$C$5,'Horas trabajadas'!$C$7,'Horas trabajadas'!$C$9,'Horas trabajadas'!$C$11,'Horas trabajadas'!$C$15)</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-E08F-41B4-9714-B12A15B28021}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Horas trabajadas'!$D$1:$D$3</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>diciembre 2025</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Número</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'Horas trabajadas'!$A$4:$A$16</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>('Horas trabajadas'!$A$4:$A$5,'Horas trabajadas'!$A$7,'Horas trabajadas'!$A$9,'Horas trabajadas'!$A$11,'Horas trabajadas'!$A$15)</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>     Abigail Peterson</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>     Anita Oliver</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>     Jennie Fletcher</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>     Marc Demo</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>     Mitchell Admin</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'Horas trabajadas'!$D$4:$D$16</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>('Horas trabajadas'!$D$4:$D$5,'Horas trabajadas'!$D$7,'Horas trabajadas'!$D$9,'Horas trabajadas'!$D$11,'Horas trabajadas'!$D$15)</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-E08F-41B4-9714-B12A15B28021}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="182"/>
+        <c:axId val="224252111"/>
+        <c:axId val="224255023"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="224252111"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="224255023"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="224255023"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="224252111"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
+  <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>266700</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>187218</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>80962</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>23</xdr:col>
-      <xdr:colOff>603421</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>58557</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>542925</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 2">
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{11FF771B-BD0F-4D91-B57F-3AD431FD0862}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{29BE341E-E54E-4206-8531-5EE3099F987F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="4724400" y="187218"/>
-          <a:ext cx="11919121" cy="5014839"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -508,64 +1607,70 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="4" width="16.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>13</v>
-      </c>
+      <c r="A1" s="1"/>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="B2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="1"/>
+        <v>1</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="D2" s="1"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="1" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="1"/>
+        <v>3</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>3</v>
+      <c r="A4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="3">
+        <v>12</v>
+      </c>
+      <c r="C4" s="3">
+        <v>4</v>
+      </c>
+      <c r="D4" s="3">
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B5" s="3">
-        <v>12</v>
-      </c>
-      <c r="C5" s="3">
         <v>4</v>
       </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
       <c r="D5" s="3">
-        <v>16</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -576,18 +1681,18 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C8">
         <v>2</v>
@@ -598,18 +1703,18 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D9" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -620,78 +1725,67 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C11">
-        <v>1</v>
+        <v>8</v>
+      </c>
+      <c r="B11">
+        <v>10</v>
       </c>
       <c r="D11" s="3">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B12">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D12" s="3">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B13">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D13" s="3">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B14">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D14" s="3">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B16">
         <v>2</v>
       </c>
       <c r="D16" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B17">
-        <v>2</v>
-      </c>
-      <c r="D17" s="3">
         <v>2</v>
       </c>
     </row>
